--- a/output/2026-10-04_17_Malesia_Sabah_ATEX_Equipment_Services.xlsx
+++ b/output/2026-10-04_17_Malesia_Sabah_ATEX_Equipment_Services.xlsx
@@ -474,7 +474,6 @@
           <t>Furse Electric (Sabah) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Kota Kinabalu, Sabah (Kepayan / SEDCO Industrial Estate, Kolombong)</t>
@@ -502,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -554,7 +553,6 @@
           <t>Essem Corporation Sdn Bhd</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Labuan (Territorio Federale adiacente a Sabah; presente nel directory fornitori del porto di Labuan)</t>
@@ -565,8 +563,6 @@
           <t>ATEX Equipment/Services - agente/distributore oil&amp;gas e marine (Alfa Laval: Air Conditioning, Compressors, Electrical, Evaporators, Desalinators, Lighting)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Parte di The Essem Group dal 1984; nominato agente ufficiale Alfa Laval per il Malaysia oil&amp;gas/marine (comunicato eco-business.com); presenza confermata come supplier nel directory del porto di Labuan (shipserv.com). Alcune fonti indicano HQ a Kuala Lumpur: localizzazione operativa a Labuan/Sabah non del tutto certa - verificare manualmente sede effettiva, telefono ed email prima del contatto.</t>
@@ -574,7 +570,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
